--- a/Data Files/OTM Test Data/BulkIDs_and_SalesOrders_Data.xlsx
+++ b/Data Files/OTM Test Data/BulkIDs_and_SalesOrders_Data.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{51A4B822-88C4-496A-BC19-642E07D9DF7E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B0EC9B-CB74-4C32-A53C-C524A42F0396}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bulk IDs Reset" r:id="rId1" sheetId="1"/>
-    <sheet name="Bulk IDs Created" r:id="rId2" sheetId="2"/>
+    <sheet name="Bulk IDs Reset" sheetId="1" r:id="rId1"/>
+    <sheet name="Bulk IDs Created" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="183">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -286,9 +286,6 @@
     <t>Unassign Successful</t>
   </si>
   <si>
-    <t>20250911-0005</t>
-  </si>
-  <si>
     <t>TENDER_UNTENDER</t>
   </si>
   <si>
@@ -565,15 +562,6 @@
     <t>SO_17551271</t>
   </si>
   <si>
-    <t>2025-09-16 00:00 America/New_York</t>
-  </si>
-  <si>
-    <t>2025-10-15 23:59 America/New_York</t>
-  </si>
-  <si>
-    <t>20250915-0002</t>
-  </si>
-  <si>
     <t>NWK</t>
   </si>
   <si>
@@ -584,13 +572,15 @@
   </si>
   <si>
     <t>20250916-0001</t>
+  </si>
+  <si>
+    <t>20250918-0001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -685,33 +675,33 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -728,10 +718,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -766,7 +756,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -818,7 +808,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -929,21 +919,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -960,7 +950,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1012,28 +1002,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:T88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
+  <dimension ref="A1:S89"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="21.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="38.36328125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="16.26953125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" width="21.36328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="26.453125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" width="22.08984375" collapsed="true"/>
+    <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="21.54296875" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="38.36328125" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.90625" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="21.36328125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="26.453125" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="22.08984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="15" r="1" s="2" spans="1:19" thickBot="1">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1059,9 +1049,9 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="15" r="2" spans="1:19" thickBot="1">
+    <row r="2" spans="1:19" ht="15" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>84</v>
@@ -1094,24 +1084,14 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
     </row>
-    <row ht="15" r="3" spans="1:19" thickBot="1">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
+    <row r="3" spans="1:19" ht="15" thickBot="1">
+      <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -1125,9 +1105,9 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
     </row>
-    <row ht="15" r="4" spans="1:19" thickBot="1">
+    <row r="4" spans="1:19" ht="15" thickBot="1">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1156,9 +1136,9 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
     </row>
-    <row ht="15" r="5" spans="1:19" thickBot="1">
+    <row r="5" spans="1:19" ht="15" thickBot="1">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1187,9 +1167,9 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row ht="15" r="6" spans="1:19" thickBot="1">
+    <row r="6" spans="1:19" ht="15" thickBot="1">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1218,9 +1198,9 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row ht="15" r="7" spans="1:19" thickBot="1">
+    <row r="7" spans="1:19" ht="15" thickBot="1">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1249,27 +1229,23 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
-    <row ht="15" r="8" spans="1:19" thickBot="1">
+    <row r="8" spans="1:19" ht="15" thickBot="1">
       <c r="A8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1284,23 +1260,27 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row ht="15" r="9" spans="1:19" thickBot="1">
+    <row r="9" spans="1:19" ht="15" thickBot="1">
       <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1315,9 +1295,9 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row ht="15" r="10" spans="1:19" thickBot="1">
+    <row r="10" spans="1:19" ht="15" thickBot="1">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1346,9 +1326,9 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row ht="15" r="11" spans="1:19" thickBot="1">
+    <row r="11" spans="1:19" ht="15" thickBot="1">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1377,31 +1357,25 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row ht="15" r="12" spans="1:19" thickBot="1">
+    <row r="12" spans="1:19" ht="15" thickBot="1">
       <c r="A12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>88</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>105</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="3"/>
@@ -1414,25 +1388,31 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row ht="15" r="13" spans="1:19" thickBot="1">
+    <row r="13" spans="1:19" ht="15" thickBot="1">
       <c r="A13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>87</v>
+      </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="4"/>
+        <v>104</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="3"/>
@@ -1445,9 +1425,9 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row ht="15" r="14" spans="1:19" thickBot="1">
+    <row r="14" spans="1:19" ht="15" thickBot="1">
       <c r="A14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1476,9 +1456,9 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row ht="15" r="15" spans="1:19" thickBot="1">
+    <row r="15" spans="1:19" ht="15" thickBot="1">
       <c r="A15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1507,9 +1487,9 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row ht="15" r="16" spans="1:19" thickBot="1">
+    <row r="16" spans="1:19" ht="15" thickBot="1">
       <c r="A16" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1538,9 +1518,9 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
     </row>
-    <row ht="15" r="17" spans="1:19" thickBot="1">
+    <row r="17" spans="1:19" ht="15" thickBot="1">
       <c r="A17" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1569,9 +1549,9 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row ht="15" r="18" spans="1:19" thickBot="1">
+    <row r="18" spans="1:19" ht="15" thickBot="1">
       <c r="A18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1600,9 +1580,9 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row ht="15" r="19" spans="1:19" thickBot="1">
+    <row r="19" spans="1:19" ht="15" thickBot="1">
       <c r="A19" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1631,9 +1611,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row ht="15" r="20" spans="1:19" thickBot="1">
+    <row r="20" spans="1:19" ht="15" thickBot="1">
       <c r="A20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1662,9 +1642,9 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row ht="15" r="21" spans="1:19" thickBot="1">
+    <row r="21" spans="1:19" ht="15" thickBot="1">
       <c r="A21" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1693,9 +1673,9 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row ht="15" r="22" spans="1:19" thickBot="1">
+    <row r="22" spans="1:19" ht="15" thickBot="1">
       <c r="A22" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1724,9 +1704,9 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row ht="15" r="23" spans="1:19" thickBot="1">
+    <row r="23" spans="1:19" ht="15" thickBot="1">
       <c r="A23" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1755,9 +1735,9 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row ht="15" r="24" spans="1:19" thickBot="1">
+    <row r="24" spans="1:19" ht="15" thickBot="1">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1786,9 +1766,9 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row ht="15" r="25" spans="1:19" thickBot="1">
+    <row r="25" spans="1:19" ht="15" thickBot="1">
       <c r="A25" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1817,9 +1797,9 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row ht="15" r="26" spans="1:19" thickBot="1">
+    <row r="26" spans="1:19" ht="15" thickBot="1">
       <c r="A26" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1848,9 +1828,9 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row ht="15" r="27" spans="1:19" thickBot="1">
+    <row r="27" spans="1:19" ht="15" thickBot="1">
       <c r="A27" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1879,9 +1859,9 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row ht="15" r="28" spans="1:19" thickBot="1">
+    <row r="28" spans="1:19" ht="15" thickBot="1">
       <c r="A28" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1910,9 +1890,9 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row ht="15" r="29" spans="1:19" thickBot="1">
+    <row r="29" spans="1:19" ht="15" thickBot="1">
       <c r="A29" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1941,9 +1921,9 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row ht="15" r="30" spans="1:19" thickBot="1">
+    <row r="30" spans="1:19" ht="15" thickBot="1">
       <c r="A30" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1972,9 +1952,9 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row ht="15" r="31" spans="1:19" thickBot="1">
+    <row r="31" spans="1:19" ht="15" thickBot="1">
       <c r="A31" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2003,9 +1983,9 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row ht="15" r="32" spans="1:19" thickBot="1">
+    <row r="32" spans="1:19" ht="15" thickBot="1">
       <c r="A32" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2034,9 +2014,9 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
-    <row ht="15" r="33" spans="1:19" thickBot="1">
+    <row r="33" spans="1:19" ht="15" thickBot="1">
       <c r="A33" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2065,9 +2045,9 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
     </row>
-    <row ht="15" r="34" spans="1:19" thickBot="1">
+    <row r="34" spans="1:19" ht="15" thickBot="1">
       <c r="A34" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2096,9 +2076,9 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
     </row>
-    <row ht="15" r="35" spans="1:19" thickBot="1">
+    <row r="35" spans="1:19" ht="15" thickBot="1">
       <c r="A35" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2127,9 +2107,9 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row ht="15" r="36" spans="1:19" thickBot="1">
+    <row r="36" spans="1:19" ht="15" thickBot="1">
       <c r="A36" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2158,9 +2138,9 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
     </row>
-    <row ht="15" r="37" spans="1:19" thickBot="1">
+    <row r="37" spans="1:19" ht="15" thickBot="1">
       <c r="A37" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2189,9 +2169,9 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
     </row>
-    <row ht="15" r="38" spans="1:19" thickBot="1">
+    <row r="38" spans="1:19" ht="15" thickBot="1">
       <c r="A38" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2220,9 +2200,9 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
     </row>
-    <row ht="15" r="39" spans="1:19" thickBot="1">
+    <row r="39" spans="1:19" ht="15" thickBot="1">
       <c r="A39" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2251,9 +2231,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
     </row>
-    <row ht="15" r="40" spans="1:19" thickBot="1">
+    <row r="40" spans="1:19" ht="15" thickBot="1">
       <c r="A40" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2282,9 +2262,9 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
     </row>
-    <row ht="15" r="41" spans="1:19" thickBot="1">
+    <row r="41" spans="1:19" ht="15" thickBot="1">
       <c r="A41" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2313,9 +2293,9 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
     </row>
-    <row ht="15" r="42" spans="1:19" thickBot="1">
+    <row r="42" spans="1:19" ht="15" thickBot="1">
       <c r="A42" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2344,9 +2324,9 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
     </row>
-    <row ht="15" r="43" spans="1:19" thickBot="1">
+    <row r="43" spans="1:19" ht="15" thickBot="1">
       <c r="A43" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -2375,9 +2355,9 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
     </row>
-    <row ht="15" r="44" spans="1:19" thickBot="1">
+    <row r="44" spans="1:19" ht="15" thickBot="1">
       <c r="A44" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2406,9 +2386,9 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
     </row>
-    <row ht="15" r="45" spans="1:19" thickBot="1">
+    <row r="45" spans="1:19" ht="15" thickBot="1">
       <c r="A45" s="4" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2437,9 +2417,9 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
     </row>
-    <row ht="15" r="46" spans="1:19" thickBot="1">
+    <row r="46" spans="1:19" ht="15" thickBot="1">
       <c r="A46" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2468,9 +2448,9 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
     </row>
-    <row ht="15" r="47" spans="1:19" thickBot="1">
+    <row r="47" spans="1:19" ht="15" thickBot="1">
       <c r="A47" s="4" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2499,9 +2479,9 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
     </row>
-    <row ht="15" r="48" spans="1:19" thickBot="1">
+    <row r="48" spans="1:19" ht="15" thickBot="1">
       <c r="A48" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2530,9 +2510,9 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
     </row>
-    <row ht="15" r="49" spans="1:19" thickBot="1">
+    <row r="49" spans="1:19" ht="15" thickBot="1">
       <c r="A49" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2561,9 +2541,9 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
     </row>
-    <row ht="15" r="50" spans="1:19" thickBot="1">
+    <row r="50" spans="1:19" ht="15" thickBot="1">
       <c r="A50" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2592,9 +2572,9 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
     </row>
-    <row ht="15" r="51" spans="1:19" thickBot="1">
+    <row r="51" spans="1:19" ht="15" thickBot="1">
       <c r="A51" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -2623,9 +2603,9 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
     </row>
-    <row ht="15" r="52" spans="1:19" thickBot="1">
+    <row r="52" spans="1:19" ht="15" thickBot="1">
       <c r="A52" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2654,9 +2634,9 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
     </row>
-    <row ht="15" r="53" spans="1:19" thickBot="1">
+    <row r="53" spans="1:19" ht="15" thickBot="1">
       <c r="A53" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2685,9 +2665,9 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
     </row>
-    <row ht="15" r="54" spans="1:19" thickBot="1">
+    <row r="54" spans="1:19" ht="15" thickBot="1">
       <c r="A54" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2716,9 +2696,9 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
     </row>
-    <row ht="15" r="55" spans="1:19" thickBot="1">
+    <row r="55" spans="1:19" ht="15" thickBot="1">
       <c r="A55" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2747,9 +2727,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
     </row>
-    <row ht="15" r="56" spans="1:19" thickBot="1">
+    <row r="56" spans="1:19" ht="15" thickBot="1">
       <c r="A56" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2778,9 +2758,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
     </row>
-    <row ht="15" r="57" spans="1:19" thickBot="1">
+    <row r="57" spans="1:19" ht="15" thickBot="1">
       <c r="A57" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2809,9 +2789,9 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
     </row>
-    <row ht="15" r="58" spans="1:19" thickBot="1">
+    <row r="58" spans="1:19" ht="15" thickBot="1">
       <c r="A58" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2840,9 +2820,9 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
     </row>
-    <row ht="15" r="59" spans="1:19" thickBot="1">
+    <row r="59" spans="1:19" ht="15" thickBot="1">
       <c r="A59" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2871,9 +2851,9 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
     </row>
-    <row ht="15" r="60" spans="1:19" thickBot="1">
+    <row r="60" spans="1:19" ht="15" thickBot="1">
       <c r="A60" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2902,9 +2882,9 @@
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
     </row>
-    <row ht="15" r="61" spans="1:19" thickBot="1">
+    <row r="61" spans="1:19" ht="15" thickBot="1">
       <c r="A61" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2933,9 +2913,9 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
     </row>
-    <row ht="15" r="62" spans="1:19" thickBot="1">
+    <row r="62" spans="1:19" ht="15" thickBot="1">
       <c r="A62" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2964,9 +2944,9 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row ht="15" r="63" spans="1:19" thickBot="1">
+    <row r="63" spans="1:19" ht="15" thickBot="1">
       <c r="A63" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2995,9 +2975,9 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
     </row>
-    <row ht="15" r="64" spans="1:19" thickBot="1">
+    <row r="64" spans="1:19" ht="15" thickBot="1">
       <c r="A64" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3026,9 +3006,9 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
     </row>
-    <row ht="15" r="65" spans="1:19" thickBot="1">
+    <row r="65" spans="1:19" ht="15" thickBot="1">
       <c r="A65" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3057,9 +3037,9 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
     </row>
-    <row ht="15" r="66" spans="1:19" thickBot="1">
+    <row r="66" spans="1:19" ht="15" thickBot="1">
       <c r="A66" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3088,9 +3068,9 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
     </row>
-    <row ht="15" r="67" spans="1:19" thickBot="1">
+    <row r="67" spans="1:19" ht="15" thickBot="1">
       <c r="A67" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3119,9 +3099,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
     </row>
-    <row ht="15" r="68" spans="1:19" thickBot="1">
+    <row r="68" spans="1:19" ht="15" thickBot="1">
       <c r="A68" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3150,9 +3130,9 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
     </row>
-    <row ht="15" r="69" spans="1:19" thickBot="1">
+    <row r="69" spans="1:19" ht="15" thickBot="1">
       <c r="A69" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3181,9 +3161,9 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
     </row>
-    <row ht="15" r="70" spans="1:19" thickBot="1">
+    <row r="70" spans="1:19" ht="15" thickBot="1">
       <c r="A70" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3212,9 +3192,9 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
     </row>
-    <row ht="15" r="71" spans="1:19" thickBot="1">
+    <row r="71" spans="1:19" ht="15" thickBot="1">
       <c r="A71" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3243,9 +3223,9 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
     </row>
-    <row ht="15" r="72" spans="1:19" thickBot="1">
+    <row r="72" spans="1:19" ht="15" thickBot="1">
       <c r="A72" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3274,9 +3254,9 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
     </row>
-    <row ht="15" r="73" spans="1:19" thickBot="1">
+    <row r="73" spans="1:19" ht="15" thickBot="1">
       <c r="A73" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3305,14 +3285,24 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
     </row>
-    <row ht="15" r="74" spans="1:19" thickBot="1">
-      <c r="A74" s="4"/>
+    <row r="74" spans="1:19" ht="15" thickBot="1">
+      <c r="A74" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
+      <c r="D74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
@@ -3326,20 +3316,29 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
     </row>
-    <row ht="15" r="75" spans="1:19" thickBot="1">
+    <row r="75" spans="1:19" ht="15" thickBot="1">
       <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
-    </row>
-    <row r="76" spans="1:19">
-      <c r="A76" s="5"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="1:19" ht="15" thickBot="1">
+      <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
@@ -3399,16 +3398,16 @@
       <c r="J80" s="5"/>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="6"/>
@@ -3494,27 +3493,39 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
     </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
-  <dimension ref="A1:F56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="39.453125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="37.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="32.90625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="25.54296875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="16.0" collapsed="true"/>
+    <col min="1" max="1" width="39.453125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="37" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="32.90625" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="25.54296875" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="16" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -3523,27 +3534,27 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3555,616 +3566,616 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D13" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D14" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D16" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D23" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D24" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D25" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D26" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D27" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D29" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D30" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D31" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D32" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D33" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E33" s="6"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D34" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D35" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D36" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D37" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D38" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E38" s="6"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D39" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E39" s="6"/>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D41" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D42" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B43" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D43" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="D44" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E44" s="6"/>
     </row>
@@ -4253,6 +4264,6 @@
       <c r="E56" s="6"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data Files/OTM Test Data/BulkIDs_and_SalesOrders_Data.xlsx
+++ b/Data Files/OTM Test Data/BulkIDs_and_SalesOrders_Data.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B0EC9B-CB74-4C32-A53C-C524A42F0396}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{400AF1EA-0A3D-45CC-BEE7-2897C78F9B40}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
+    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Bulk IDs Reset" sheetId="1" r:id="rId1"/>
-    <sheet name="Bulk IDs Created" sheetId="2" r:id="rId2"/>
+    <sheet name="Bulk IDs Reset" r:id="rId1" sheetId="1"/>
+    <sheet name="Bulk IDs Created" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="183">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -581,6 +581,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -675,33 +676,33 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -718,10 +719,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -756,7 +757,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -808,7 +809,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -919,21 +920,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -950,7 +951,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1002,28 +1003,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:S89"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
+  <dimension ref="A1:T89"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="21.54296875" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="38.36328125" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="16.26953125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.90625" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="21.36328125" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="26.453125" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="22.08984375" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="21.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="38.36328125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="16.26953125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="21.36328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="26.453125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" width="22.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="15" thickBot="1">
+    <row customFormat="1" ht="15" r="1" s="2" spans="1:19" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +1050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="2" spans="1:19" thickBot="1">
       <c r="A2" s="4" t="s">
         <v>182</v>
       </c>
@@ -1066,10 +1067,10 @@
         <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -1084,7 +1085,7 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="3" spans="1:19" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1105,7 +1106,7 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="4" spans="1:19" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -1136,7 +1137,7 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="5" spans="1:19" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1167,7 +1168,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="6" spans="1:19" thickBot="1">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -1198,7 +1199,7 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="7" spans="1:19" thickBot="1">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -1229,7 +1230,7 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="8" spans="1:19" thickBot="1">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -1260,7 +1261,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="9" spans="1:19" thickBot="1">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1295,7 +1296,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="10" spans="1:19" thickBot="1">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1326,7 +1327,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="11" spans="1:19" thickBot="1">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1357,7 +1358,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="12" spans="1:19" thickBot="1">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -1388,7 +1389,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="13" spans="1:19" thickBot="1">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1425,7 +1426,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="14" spans="1:19" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>23</v>
       </c>
@@ -1456,7 +1457,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="15" spans="1:19" thickBot="1">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1487,7 +1488,7 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="16" spans="1:19" thickBot="1">
       <c r="A16" s="4" t="s">
         <v>25</v>
       </c>
@@ -1518,7 +1519,7 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
     </row>
-    <row r="17" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="17" spans="1:19" thickBot="1">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -1549,7 +1550,7 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="18" spans="1:19" thickBot="1">
       <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
@@ -1580,7 +1581,7 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="19" spans="1:19" thickBot="1">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -1611,7 +1612,7 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="20" spans="1:19" thickBot="1">
       <c r="A20" s="4" t="s">
         <v>29</v>
       </c>
@@ -1642,7 +1643,7 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="21" spans="1:19" thickBot="1">
       <c r="A21" s="4" t="s">
         <v>30</v>
       </c>
@@ -1673,7 +1674,7 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="22" spans="1:19" thickBot="1">
       <c r="A22" s="4" t="s">
         <v>31</v>
       </c>
@@ -1704,7 +1705,7 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="23" spans="1:19" thickBot="1">
       <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
@@ -1735,7 +1736,7 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="24" spans="1:19" thickBot="1">
       <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
@@ -1766,7 +1767,7 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="25" spans="1:19" thickBot="1">
       <c r="A25" s="4" t="s">
         <v>34</v>
       </c>
@@ -1797,7 +1798,7 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="26" spans="1:19" thickBot="1">
       <c r="A26" s="4" t="s">
         <v>35</v>
       </c>
@@ -1828,7 +1829,7 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="27" spans="1:19" thickBot="1">
       <c r="A27" s="4" t="s">
         <v>36</v>
       </c>
@@ -1859,7 +1860,7 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="28" spans="1:19" thickBot="1">
       <c r="A28" s="4" t="s">
         <v>37</v>
       </c>
@@ -1890,7 +1891,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="29" spans="1:19" thickBot="1">
       <c r="A29" s="4" t="s">
         <v>38</v>
       </c>
@@ -1921,7 +1922,7 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="30" spans="1:19" thickBot="1">
       <c r="A30" s="4" t="s">
         <v>39</v>
       </c>
@@ -1952,7 +1953,7 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="31" spans="1:19" thickBot="1">
       <c r="A31" s="4" t="s">
         <v>40</v>
       </c>
@@ -1983,7 +1984,7 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row r="32" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="32" spans="1:19" thickBot="1">
       <c r="A32" s="4" t="s">
         <v>41</v>
       </c>
@@ -2014,7 +2015,7 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
-    <row r="33" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="33" spans="1:19" thickBot="1">
       <c r="A33" s="4" t="s">
         <v>42</v>
       </c>
@@ -2045,7 +2046,7 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
     </row>
-    <row r="34" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="34" spans="1:19" thickBot="1">
       <c r="A34" s="4" t="s">
         <v>43</v>
       </c>
@@ -2076,7 +2077,7 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
     </row>
-    <row r="35" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="35" spans="1:19" thickBot="1">
       <c r="A35" s="4" t="s">
         <v>44</v>
       </c>
@@ -2107,7 +2108,7 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="36" spans="1:19" thickBot="1">
       <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
@@ -2138,7 +2139,7 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
     </row>
-    <row r="37" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="37" spans="1:19" thickBot="1">
       <c r="A37" s="4" t="s">
         <v>46</v>
       </c>
@@ -2169,7 +2170,7 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
     </row>
-    <row r="38" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="38" spans="1:19" thickBot="1">
       <c r="A38" s="4" t="s">
         <v>47</v>
       </c>
@@ -2200,7 +2201,7 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
     </row>
-    <row r="39" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="39" spans="1:19" thickBot="1">
       <c r="A39" s="4" t="s">
         <v>48</v>
       </c>
@@ -2231,7 +2232,7 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
     </row>
-    <row r="40" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="40" spans="1:19" thickBot="1">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -2262,7 +2263,7 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
     </row>
-    <row r="41" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="41" spans="1:19" thickBot="1">
       <c r="A41" s="4" t="s">
         <v>50</v>
       </c>
@@ -2293,7 +2294,7 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
     </row>
-    <row r="42" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="42" spans="1:19" thickBot="1">
       <c r="A42" s="4" t="s">
         <v>51</v>
       </c>
@@ -2324,7 +2325,7 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
     </row>
-    <row r="43" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="43" spans="1:19" thickBot="1">
       <c r="A43" s="4" t="s">
         <v>52</v>
       </c>
@@ -2355,7 +2356,7 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
     </row>
-    <row r="44" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="44" spans="1:19" thickBot="1">
       <c r="A44" s="4" t="s">
         <v>53</v>
       </c>
@@ -2386,7 +2387,7 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
     </row>
-    <row r="45" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="45" spans="1:19" thickBot="1">
       <c r="A45" s="4" t="s">
         <v>54</v>
       </c>
@@ -2417,7 +2418,7 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
     </row>
-    <row r="46" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="46" spans="1:19" thickBot="1">
       <c r="A46" s="4" t="s">
         <v>18</v>
       </c>
@@ -2448,7 +2449,7 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
     </row>
-    <row r="47" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="47" spans="1:19" thickBot="1">
       <c r="A47" s="4" t="s">
         <v>19</v>
       </c>
@@ -2479,7 +2480,7 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
     </row>
-    <row r="48" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="48" spans="1:19" thickBot="1">
       <c r="A48" s="4" t="s">
         <v>55</v>
       </c>
@@ -2510,7 +2511,7 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
     </row>
-    <row r="49" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="49" spans="1:19" thickBot="1">
       <c r="A49" s="4" t="s">
         <v>56</v>
       </c>
@@ -2541,7 +2542,7 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
     </row>
-    <row r="50" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="50" spans="1:19" thickBot="1">
       <c r="A50" s="4" t="s">
         <v>57</v>
       </c>
@@ -2572,7 +2573,7 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
     </row>
-    <row r="51" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="51" spans="1:19" thickBot="1">
       <c r="A51" s="4" t="s">
         <v>58</v>
       </c>
@@ -2603,7 +2604,7 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
     </row>
-    <row r="52" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="52" spans="1:19" thickBot="1">
       <c r="A52" s="4" t="s">
         <v>59</v>
       </c>
@@ -2634,7 +2635,7 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
     </row>
-    <row r="53" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="53" spans="1:19" thickBot="1">
       <c r="A53" s="4" t="s">
         <v>60</v>
       </c>
@@ -2665,7 +2666,7 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
     </row>
-    <row r="54" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="54" spans="1:19" thickBot="1">
       <c r="A54" s="4" t="s">
         <v>61</v>
       </c>
@@ -2696,7 +2697,7 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
     </row>
-    <row r="55" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="55" spans="1:19" thickBot="1">
       <c r="A55" s="4" t="s">
         <v>62</v>
       </c>
@@ -2727,7 +2728,7 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
     </row>
-    <row r="56" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="56" spans="1:19" thickBot="1">
       <c r="A56" s="4" t="s">
         <v>63</v>
       </c>
@@ -2758,7 +2759,7 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
     </row>
-    <row r="57" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="57" spans="1:19" thickBot="1">
       <c r="A57" s="4" t="s">
         <v>64</v>
       </c>
@@ -2789,7 +2790,7 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
     </row>
-    <row r="58" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="58" spans="1:19" thickBot="1">
       <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
@@ -2820,7 +2821,7 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
     </row>
-    <row r="59" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="59" spans="1:19" thickBot="1">
       <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
@@ -2851,7 +2852,7 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
     </row>
-    <row r="60" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="60" spans="1:19" thickBot="1">
       <c r="A60" s="4" t="s">
         <v>67</v>
       </c>
@@ -2882,7 +2883,7 @@
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
     </row>
-    <row r="61" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="61" spans="1:19" thickBot="1">
       <c r="A61" s="4" t="s">
         <v>68</v>
       </c>
@@ -2913,7 +2914,7 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
     </row>
-    <row r="62" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="62" spans="1:19" thickBot="1">
       <c r="A62" s="4" t="s">
         <v>69</v>
       </c>
@@ -2944,7 +2945,7 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
     </row>
-    <row r="63" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="63" spans="1:19" thickBot="1">
       <c r="A63" s="4" t="s">
         <v>70</v>
       </c>
@@ -2975,7 +2976,7 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
     </row>
-    <row r="64" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="64" spans="1:19" thickBot="1">
       <c r="A64" s="4" t="s">
         <v>71</v>
       </c>
@@ -3006,7 +3007,7 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
     </row>
-    <row r="65" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="65" spans="1:19" thickBot="1">
       <c r="A65" s="4" t="s">
         <v>72</v>
       </c>
@@ -3037,7 +3038,7 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
     </row>
-    <row r="66" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="66" spans="1:19" thickBot="1">
       <c r="A66" s="4" t="s">
         <v>73</v>
       </c>
@@ -3068,7 +3069,7 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
     </row>
-    <row r="67" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="67" spans="1:19" thickBot="1">
       <c r="A67" s="4" t="s">
         <v>74</v>
       </c>
@@ -3099,7 +3100,7 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
     </row>
-    <row r="68" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="68" spans="1:19" thickBot="1">
       <c r="A68" s="4" t="s">
         <v>75</v>
       </c>
@@ -3130,7 +3131,7 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
     </row>
-    <row r="69" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="69" spans="1:19" thickBot="1">
       <c r="A69" s="4" t="s">
         <v>76</v>
       </c>
@@ -3161,7 +3162,7 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
     </row>
-    <row r="70" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="70" spans="1:19" thickBot="1">
       <c r="A70" s="4" t="s">
         <v>77</v>
       </c>
@@ -3192,7 +3193,7 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
     </row>
-    <row r="71" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="71" spans="1:19" thickBot="1">
       <c r="A71" s="4" t="s">
         <v>78</v>
       </c>
@@ -3223,7 +3224,7 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
     </row>
-    <row r="72" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="72" spans="1:19" thickBot="1">
       <c r="A72" s="4" t="s">
         <v>79</v>
       </c>
@@ -3254,7 +3255,7 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
     </row>
-    <row r="73" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="73" spans="1:19" thickBot="1">
       <c r="A73" s="4" t="s">
         <v>80</v>
       </c>
@@ -3285,7 +3286,7 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="74" spans="1:19" thickBot="1">
       <c r="A74" s="4" t="s">
         <v>81</v>
       </c>
@@ -3316,7 +3317,7 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
     </row>
-    <row r="75" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="75" spans="1:19" thickBot="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3337,7 +3338,7 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
     </row>
-    <row r="76" spans="1:19" ht="15" thickBot="1">
+    <row ht="15" r="76" spans="1:19" thickBot="1">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3506,21 +3507,21 @@
       <c r="J89" s="6"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
-  <dimension ref="A1:E56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="37" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="32.90625" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="25.54296875" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="16" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="39.453125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="37.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="32.90625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="25.54296875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="16.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4264,6 +4265,6 @@
       <c r="E56" s="6"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>